--- a/output/quickfixclose5_all_markets_daily.xlsx
+++ b/output/quickfixclose5_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose5_all_markets_daily.xlsx
+++ b/output/quickfixclose5_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -639,31 +639,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -675,43 +675,43 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>22.96</v>
+        <v>24.3</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>122959.25</v>
+        <v>124303.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -723,19 +723,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16.39</v>
+        <v>22.96</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>116390.14</v>
+        <v>122959.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -746,20 +746,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -771,19 +771,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15.37</v>
+        <v>16.39</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>115368.74</v>
+        <v>116390.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -794,17 +794,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -822,16 +822,16 @@
         <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10.13</v>
+        <v>15.37</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>110130.43</v>
+        <v>115368.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -842,20 +842,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>109961.07</v>
+        <v>110130.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -890,20 +890,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -912,47 +912,47 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>50</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.4</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106395.88</v>
+        <v>109961.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -963,43 +963,43 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.3</v>
+        <v>5.33</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>104299.62</v>
+        <v>105331.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.81</v>
+        <v>4.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102814.99</v>
+        <v>104299.62</v>
       </c>
     </row>
     <row r="12">
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>
@@ -5482,22 +5482,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>4</v>
+      </c>
       <c r="G54" t="n">
         <v>2.69</v>
       </c>
       <c r="H54" t="n">
         <v>2.665</v>
       </c>
+      <c r="J54" t="n">
+        <v>2.665</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N54" t="n">
         <v>106395.88</v>
       </c>
       <c r="O54" t="n">
-        <v>106395.88</v>
+        <v>105331.92</v>
       </c>
     </row>
     <row r="55">
@@ -7031,22 +7048,39 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
       <c r="G83" t="n">
         <v>101.411</v>
       </c>
       <c r="H83" t="n">
         <v>101.491</v>
       </c>
+      <c r="J83" t="n">
+        <v>99.739</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>20.9</v>
       </c>
       <c r="N83" t="n">
         <v>102814.99</v>
       </c>
       <c r="O83" t="n">
-        <v>102814.99</v>
+        <v>124303.33</v>
       </c>
     </row>
     <row r="84">

--- a/output/quickfixclose5_all_markets_daily.xlsx
+++ b/output/quickfixclose5_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>62.5</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4872,11 +4872,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4885,48 +4885,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>3</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G43" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0.006454</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.006454</v>
+        <v>4363.8</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N43" t="n">
-        <v>100000</v>
+        <v>126333.15</v>
       </c>
       <c r="O43" t="n">
-        <v>99000</v>
+        <v>126333.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -4939,25 +4922,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H44" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="J44" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -4984,7 +4967,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4993,42 +4976,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H45" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="J45" t="n">
-        <v>245.22</v>
+        <v>239.73</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>19.2727</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>19.2727</v>
+        <v>-1</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N45" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O45" t="n">
         <v>99000</v>
-      </c>
-      <c r="O45" t="n">
-        <v>118080</v>
       </c>
     </row>
     <row r="46">
@@ -5038,7 +5021,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5047,25 +5030,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H46" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="J46" t="n">
-        <v>248.9</v>
+        <v>245.22</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5073,16 +5056,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.184</v>
+        <v>19.2727</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5.184</v>
+        <v>19.2727</v>
       </c>
       <c r="N46" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O46" t="n">
         <v>118080</v>
-      </c>
-      <c r="O46" t="n">
-        <v>124201.27</v>
       </c>
     </row>
     <row r="47">
@@ -5092,61 +5075,61 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H47" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="J47" t="n">
-        <v>234.36</v>
+        <v>248.9</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v>-1</v>
+        <v>5.184</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>5.184</v>
       </c>
       <c r="N47" t="n">
+        <v>118080</v>
+      </c>
+      <c r="O47" t="n">
         <v>124201.27</v>
-      </c>
-      <c r="O47" t="n">
-        <v>122959.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5155,25 +5138,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H48" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="J48" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5187,10 +5170,10 @@
         <v>-1</v>
       </c>
       <c r="N48" t="n">
-        <v>100000</v>
+        <v>124201.27</v>
       </c>
       <c r="O48" t="n">
-        <v>99000</v>
+        <v>122959.25</v>
       </c>
     </row>
     <row r="49">
@@ -5200,7 +5183,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5209,12 +5192,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5224,10 +5207,10 @@
         <v>5.7714</v>
       </c>
       <c r="H49" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="J49" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5241,10 +5224,10 @@
         <v>-1</v>
       </c>
       <c r="N49" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O49" t="n">
         <v>99000</v>
-      </c>
-      <c r="O49" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="50">
@@ -5254,7 +5237,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5263,42 +5246,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H50" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="J50" t="n">
-        <v>5.502</v>
+        <v>5.6774</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.7997</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>2.7997</v>
+        <v>-1</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N50" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O50" t="n">
         <v>98010</v>
-      </c>
-      <c r="O50" t="n">
-        <v>100753.99</v>
       </c>
     </row>
     <row r="51">
@@ -5308,61 +5291,61 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H51" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="J51" t="n">
-        <v>6.1481</v>
+        <v>5.502</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>-1</v>
+        <v>2.7997</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2.7997</v>
       </c>
       <c r="N51" t="n">
+        <v>98010</v>
+      </c>
+      <c r="O51" t="n">
         <v>100753.99</v>
-      </c>
-      <c r="O51" t="n">
-        <v>99746.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5371,25 +5354,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H52" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="J52" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5403,10 +5386,10 @@
         <v>-1</v>
       </c>
       <c r="N52" t="n">
-        <v>100000</v>
+        <v>100753.99</v>
       </c>
       <c r="O52" t="n">
-        <v>99000</v>
+        <v>99746.45</v>
       </c>
     </row>
     <row r="53">
@@ -5416,7 +5399,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5425,42 +5408,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>3.305</v>
       </c>
       <c r="H53" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J53" t="n">
-        <v>2.924</v>
+        <v>3.354</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>7.4706</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>7.4706</v>
+        <v>-1</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N53" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O53" t="n">
         <v>99000</v>
-      </c>
-      <c r="O53" t="n">
-        <v>106395.88</v>
       </c>
     </row>
     <row r="54">
@@ -5470,61 +5453,61 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H54" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J54" t="n">
-        <v>2.665</v>
+        <v>2.924</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+        <v>7.4706</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>7.4706</v>
       </c>
       <c r="N54" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O54" t="n">
         <v>106395.88</v>
-      </c>
-      <c r="O54" t="n">
-        <v>105331.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5533,42 +5516,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H55" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J55" t="n">
-        <v>1382.6</v>
+        <v>2.665</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.3059</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>1.3059</v>
+        <v>-1</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N55" t="n">
-        <v>100000</v>
+        <v>106395.88</v>
       </c>
       <c r="O55" t="n">
-        <v>101305.88</v>
+        <v>105331.92</v>
       </c>
     </row>
     <row r="56">
@@ -5578,7 +5561,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5587,25 +5570,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H56" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J56" t="n">
-        <v>1272.5</v>
+        <v>1382.6</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5613,70 +5596,70 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>13.8816</v>
+        <v>1.3059</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>13.8816</v>
+        <v>1.3059</v>
       </c>
       <c r="N56" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O56" t="n">
         <v>101305.88</v>
-      </c>
-      <c r="O56" t="n">
-        <v>115368.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H57" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2113.7</v>
+        <v>1272.5</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>-1</v>
+        <v>13.8816</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>13.8816</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>101305.88</v>
       </c>
       <c r="O57" t="n">
-        <v>99000</v>
+        <v>115368.74</v>
       </c>
     </row>
     <row r="58">
@@ -5686,34 +5669,34 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>2</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
       <c r="G58" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H58" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J58" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5727,10 +5710,10 @@
         <v>-1</v>
       </c>
       <c r="N58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O58" t="n">
         <v>99000</v>
-      </c>
-      <c r="O58" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="59">
@@ -5740,7 +5723,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5749,25 +5732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H59" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J59" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5781,47 +5764,47 @@
         <v>-1</v>
       </c>
       <c r="N59" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O59" t="n">
         <v>98010</v>
-      </c>
-      <c r="O59" t="n">
-        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>27907</v>
+        <v>1581.5</v>
       </c>
       <c r="H60" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="J60" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5835,20 +5818,20 @@
         <v>-1</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O60" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5857,48 +5840,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>2</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G61" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H61" t="n">
-        <v>7223.26</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N61" t="n">
-        <v>100000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O61" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -5911,25 +5877,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H62" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="J62" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5952,7 +5918,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5965,52 +5931,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G63" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H63" t="n">
-        <v>6988.83</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7002</v>
+        <v>30074.01</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>-3.0482</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N63" t="n">
         <v>99000</v>
       </c>
       <c r="O63" t="n">
-        <v>95982.27</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6019,25 +5968,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H64" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="J64" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6051,20 +6000,20 @@
         <v>-1</v>
       </c>
       <c r="N64" t="n">
-        <v>95982.27</v>
+        <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6073,42 +6022,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G65" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H65" t="n">
-        <v>6986.84</v>
-      </c>
-      <c r="J65" t="n">
-        <v>6986.84</v>
+        <v>7820.26</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N65" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
       <c r="O65" t="n">
-        <v>94072.22</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="66">
@@ -6118,34 +6050,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>6794.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H66" t="n">
-        <v>6770.77</v>
+        <v>6965.7</v>
       </c>
       <c r="J66" t="n">
-        <v>6769.03</v>
+        <v>6965.7</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6153,26 +6085,26 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N66" t="n">
-        <v>94072.22</v>
+        <v>100000</v>
       </c>
       <c r="O66" t="n">
-        <v>93062.23</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6181,25 +6113,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>88.001</v>
+        <v>6988.83</v>
       </c>
       <c r="J67" t="n">
-        <v>88.001</v>
+        <v>7002</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6207,53 +6139,53 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N67" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O67" t="n">
-        <v>99000</v>
+        <v>95982.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="J68" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6267,20 +6199,20 @@
         <v>-1</v>
       </c>
       <c r="N68" t="n">
-        <v>99000</v>
+        <v>95982.27</v>
       </c>
       <c r="O68" t="n">
-        <v>98010</v>
+        <v>95022.45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6289,25 +6221,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="J69" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6321,47 +6253,47 @@
         <v>-1</v>
       </c>
       <c r="N69" t="n">
-        <v>100000</v>
+        <v>95022.45</v>
       </c>
       <c r="O69" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H70" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="J70" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6369,22 +6301,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>94072.22</v>
       </c>
       <c r="O70" t="n">
-        <v>98944.44</v>
+        <v>93062.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6397,25 +6329,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6438,7 +6370,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6446,30 +6378,30 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6492,61 +6424,61 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8498</v>
+        <v>15.26</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N73" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6559,25 +6491,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H74" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="J74" t="n">
-        <v>116.79</v>
+        <v>21.08</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6585,26 +6517,26 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>99000</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6613,25 +6545,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="J75" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6645,47 +6577,47 @@
         <v>-1</v>
       </c>
       <c r="N75" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O75" t="n">
         <v>99000</v>
-      </c>
-      <c r="O75" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="J76" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6699,74 +6631,74 @@
         <v>-1</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O76" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>99.376</v>
+        <v>0.8467</v>
       </c>
       <c r="H77" t="n">
-        <v>99.571</v>
+        <v>0.8436</v>
       </c>
       <c r="J77" t="n">
-        <v>99.149</v>
+        <v>0.8498</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.1641</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1.1641</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O77" t="n">
-        <v>100152.46</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6775,25 +6707,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>99.246</v>
+        <v>116.5</v>
       </c>
       <c r="H78" t="n">
-        <v>99.501</v>
+        <v>116.79</v>
       </c>
       <c r="J78" t="n">
-        <v>99.501</v>
+        <v>116.79</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6807,20 +6739,20 @@
         <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>100152.46</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>99150.94</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6829,25 +6761,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>100.066</v>
+        <v>118.02</v>
       </c>
       <c r="H79" t="n">
-        <v>100.201</v>
+        <v>118.16</v>
       </c>
       <c r="J79" t="n">
-        <v>100.201</v>
+        <v>118.16</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6861,10 +6793,10 @@
         <v>-1</v>
       </c>
       <c r="N79" t="n">
-        <v>99150.94</v>
+        <v>99000</v>
       </c>
       <c r="O79" t="n">
-        <v>98159.42999999999</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="80">
@@ -6874,34 +6806,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>100.361</v>
+        <v>97.569</v>
       </c>
       <c r="J80" t="n">
-        <v>100.361</v>
+        <v>97.569</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6915,10 +6847,10 @@
         <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>98159.42999999999</v>
+        <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>97177.83</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="81">
@@ -6928,7 +6860,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6937,42 +6869,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>100.621</v>
+        <v>99.376</v>
       </c>
       <c r="H81" t="n">
-        <v>100.911</v>
+        <v>99.571</v>
       </c>
       <c r="J81" t="n">
-        <v>100.911</v>
+        <v>99.149</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>-1</v>
+        <v>1.1641</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1.1641</v>
       </c>
       <c r="N81" t="n">
-        <v>97177.83</v>
+        <v>99000</v>
       </c>
       <c r="O81" t="n">
-        <v>96206.05</v>
+        <v>100152.46</v>
       </c>
     </row>
     <row r="82">
@@ -6982,7 +6914,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6991,42 +6923,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>101.411</v>
+        <v>99.246</v>
       </c>
       <c r="H82" t="n">
-        <v>101.526</v>
+        <v>99.501</v>
       </c>
       <c r="J82" t="n">
-        <v>100.621</v>
+        <v>99.501</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>6.8696</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>6.8696</v>
+        <v>-1</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N82" t="n">
-        <v>96206.05</v>
+        <v>100152.46</v>
       </c>
       <c r="O82" t="n">
-        <v>102814.99</v>
+        <v>99150.94</v>
       </c>
     </row>
     <row r="83">
@@ -7036,7 +6968,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -7045,52 +6977,52 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G83" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H83" t="n">
-        <v>101.491</v>
+        <v>100.201</v>
       </c>
       <c r="J83" t="n">
-        <v>99.739</v>
+        <v>100.201</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>20.9</v>
+        <v>-1</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N83" t="n">
-        <v>102814.99</v>
+        <v>99150.94</v>
       </c>
       <c r="O83" t="n">
-        <v>124303.33</v>
+        <v>98159.42999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7099,25 +7031,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H84" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="J84" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7131,20 +7063,20 @@
         <v>-1</v>
       </c>
       <c r="N84" t="n">
-        <v>100000</v>
+        <v>98159.42999999999</v>
       </c>
       <c r="O84" t="n">
-        <v>99000</v>
+        <v>97177.83</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7153,41 +7085,257 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>2</v>
       </c>
       <c r="G85" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H85" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="J85" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>97177.83</v>
+      </c>
+      <c r="O85" t="n">
+        <v>96206.05</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H86" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J86" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>6.8696</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>6.8696</v>
+      </c>
+      <c r="N86" t="n">
+        <v>96206.05</v>
+      </c>
+      <c r="O86" t="n">
+        <v>102814.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>8</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H87" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J87" t="n">
+        <v>99.739</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N87" t="n">
+        <v>102814.99</v>
+      </c>
+      <c r="O87" t="n">
+        <v>124303.33</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H88" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J88" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O88" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
         <v>130.16</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H89" t="n">
         <v>130.94</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J89" t="n">
         <v>139.27</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="L85" t="n">
+      <c r="L89" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M85" s="5" t="n">
+      <c r="M89" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N89" t="n">
         <v>99000</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O89" t="n">
         <v>87437.31</v>
       </c>
     </row>

--- a/output/quickfixclose5_all_markets_daily.xlsx
+++ b/output/quickfixclose5_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,20 +602,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26.33</v>
+        <v>25.07</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>126333.15</v>
+        <v>125069.82</v>
       </c>
     </row>
     <row r="4">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>25</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixclose5 daily (exit = the close of price bar 5), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4888,22 +4888,39 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
       <c r="G43" t="n">
         <v>4305.3</v>
       </c>
       <c r="H43" t="n">
         <v>4363.8</v>
       </c>
+      <c r="J43" t="n">
+        <v>4363.8</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N43" t="n">
         <v>126333.15</v>
       </c>
       <c r="O43" t="n">
-        <v>126333.15</v>
+        <v>125069.82</v>
       </c>
     </row>
     <row r="44">
@@ -5395,11 +5412,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5408,42 +5425,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G53" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H53" t="n">
-        <v>3.354</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N53" t="n">
-        <v>100000</v>
+        <v>99746.45</v>
       </c>
       <c r="O53" t="n">
-        <v>99000</v>
+        <v>99746.45</v>
       </c>
     </row>
     <row r="54">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5462,42 +5462,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>3.305</v>
       </c>
       <c r="H54" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J54" t="n">
-        <v>2.924</v>
+        <v>3.354</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>7.4706</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>7.4706</v>
+        <v>-1</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N54" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O54" t="n">
         <v>99000</v>
-      </c>
-      <c r="O54" t="n">
-        <v>106395.88</v>
       </c>
     </row>
     <row r="55">
@@ -5507,61 +5507,61 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H55" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J55" t="n">
-        <v>2.665</v>
+        <v>2.924</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>-1</v>
+        <v>7.4706</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>7.4706</v>
       </c>
       <c r="N55" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O55" t="n">
         <v>106395.88</v>
-      </c>
-      <c r="O55" t="n">
-        <v>105331.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5570,42 +5570,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H56" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J56" t="n">
-        <v>1382.6</v>
+        <v>2.665</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.3059</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>1.3059</v>
+        <v>-1</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>106395.88</v>
       </c>
       <c r="O56" t="n">
-        <v>101305.88</v>
+        <v>105331.92</v>
       </c>
     </row>
     <row r="57">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5624,25 +5624,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H57" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J57" t="n">
-        <v>1272.5</v>
+        <v>1382.6</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5650,124 +5650,107 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>13.8816</v>
+        <v>1.3059</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13.8816</v>
+        <v>1.3059</v>
       </c>
       <c r="N57" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O57" t="n">
         <v>101305.88</v>
-      </c>
-      <c r="O57" t="n">
-        <v>115368.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H58" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2113.7</v>
+        <v>1272.5</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>-1</v>
+        <v>13.8816</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>13.8816</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>101305.88</v>
       </c>
       <c r="O58" t="n">
-        <v>99000</v>
+        <v>115368.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G59" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1621</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N59" t="n">
-        <v>99000</v>
+        <v>115368.74</v>
       </c>
       <c r="O59" t="n">
-        <v>98010</v>
+        <v>115368.74</v>
       </c>
     </row>
     <row r="60">
@@ -5777,34 +5760,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H60" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="J60" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5818,10 +5801,10 @@
         <v>-1</v>
       </c>
       <c r="N60" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="61">
@@ -5831,71 +5814,88 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1769.6</v>
+        <v>1641.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1798.4</v>
+        <v>1621</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1621</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N61" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O61" t="n">
-        <v>97029.89999999999</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>27907</v>
+        <v>1581.5</v>
       </c>
       <c r="H62" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="J62" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
         <v>-1</v>
       </c>
       <c r="N62" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O62" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H63" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5946,16 +5946,16 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -5968,25 +5968,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H64" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J64" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>7773</v>
+        <v>29892.8</v>
       </c>
       <c r="H65" t="n">
-        <v>7820.26</v>
+        <v>30074.01</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6059,25 +6059,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H66" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="J66" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6113,42 +6113,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G67" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H67" t="n">
-        <v>6988.83</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7002</v>
+        <v>7820.26</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-3.0482</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N67" t="n">
         <v>99000</v>
       </c>
       <c r="O67" t="n">
-        <v>95982.27</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="68">
@@ -6158,7 +6141,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6167,25 +6150,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H68" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="J68" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6199,10 +6182,10 @@
         <v>-1</v>
       </c>
       <c r="N68" t="n">
-        <v>95982.27</v>
+        <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="69">
@@ -6212,7 +6195,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6221,12 +6204,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -6236,10 +6219,10 @@
         <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="J69" t="n">
-        <v>6986.84</v>
+        <v>7002</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6247,16 +6230,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N69" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
       <c r="O69" t="n">
-        <v>94072.22</v>
+        <v>95982.27</v>
       </c>
     </row>
     <row r="70">
@@ -6266,34 +6249,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H70" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="J70" t="n">
-        <v>6769.03</v>
+        <v>6992.85</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6301,26 +6284,26 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N70" t="n">
-        <v>94072.22</v>
+        <v>95982.27</v>
       </c>
       <c r="O70" t="n">
-        <v>93062.23</v>
+        <v>95022.45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6329,25 +6312,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="J71" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6361,20 +6344,20 @@
         <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>95022.45</v>
       </c>
       <c r="O71" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6383,25 +6366,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H72" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="J72" t="n">
-        <v>71.999</v>
+        <v>6769.03</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6409,22 +6392,22 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="N72" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
       <c r="O72" t="n">
-        <v>98010</v>
+        <v>93062.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6437,25 +6420,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H73" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="J73" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6478,38 +6461,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="J74" t="n">
-        <v>21.08</v>
+        <v>71.999</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6517,22 +6500,22 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O74" t="n">
-        <v>98944.44</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6545,25 +6528,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6586,11 +6569,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6599,25 +6582,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8658</v>
+        <v>21.08</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6625,16 +6608,16 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N76" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>98010</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="77">
@@ -6644,61 +6627,61 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N77" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6707,25 +6690,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="J78" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6739,70 +6722,70 @@
         <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O78" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H79" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="J79" t="n">
-        <v>118.16</v>
+        <v>0.8498</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O79" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -6810,30 +6793,30 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H80" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="J80" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6856,7 +6839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -6869,42 +6852,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G81" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H81" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="J81" t="n">
-        <v>99.149</v>
+        <v>118.16</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.1641</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>1.1641</v>
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N81" t="n">
         <v>99000</v>
       </c>
       <c r="O81" t="n">
-        <v>100152.46</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="82">
@@ -6914,34 +6897,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>99.246</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>99.501</v>
+        <v>97.569</v>
       </c>
       <c r="J82" t="n">
-        <v>99.501</v>
+        <v>97.569</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6955,10 +6938,10 @@
         <v>-1</v>
       </c>
       <c r="N82" t="n">
-        <v>100152.46</v>
+        <v>100000</v>
       </c>
       <c r="O82" t="n">
-        <v>99150.94</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="83">
@@ -6968,7 +6951,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6977,42 +6960,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H83" t="n">
-        <v>100.201</v>
+        <v>99.571</v>
       </c>
       <c r="J83" t="n">
-        <v>100.201</v>
+        <v>99.149</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v>-1</v>
+        <v>1.1641</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1.1641</v>
       </c>
       <c r="N83" t="n">
-        <v>99150.94</v>
+        <v>99000</v>
       </c>
       <c r="O83" t="n">
-        <v>98159.42999999999</v>
+        <v>100152.46</v>
       </c>
     </row>
     <row r="84">
@@ -7022,7 +7005,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7031,25 +7014,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H84" t="n">
-        <v>100.361</v>
+        <v>99.501</v>
       </c>
       <c r="J84" t="n">
-        <v>100.361</v>
+        <v>99.501</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7063,10 +7046,10 @@
         <v>-1</v>
       </c>
       <c r="N84" t="n">
-        <v>98159.42999999999</v>
+        <v>100152.46</v>
       </c>
       <c r="O84" t="n">
-        <v>97177.83</v>
+        <v>99150.94</v>
       </c>
     </row>
     <row r="85">
@@ -7076,7 +7059,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7085,25 +7068,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H85" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="J85" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7117,10 +7100,10 @@
         <v>-1</v>
       </c>
       <c r="N85" t="n">
-        <v>97177.83</v>
+        <v>99150.94</v>
       </c>
       <c r="O85" t="n">
-        <v>96206.05</v>
+        <v>98159.42999999999</v>
       </c>
     </row>
     <row r="86">
@@ -7130,7 +7113,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7139,42 +7122,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H86" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="J86" t="n">
-        <v>100.621</v>
+        <v>100.361</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>6.8696</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>6.8696</v>
+        <v>-1</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N86" t="n">
-        <v>96206.05</v>
+        <v>98159.42999999999</v>
       </c>
       <c r="O86" t="n">
-        <v>102814.99</v>
+        <v>97177.83</v>
       </c>
     </row>
     <row r="87">
@@ -7184,7 +7167,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7193,52 +7176,52 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H87" t="n">
-        <v>101.491</v>
+        <v>100.911</v>
       </c>
       <c r="J87" t="n">
-        <v>99.739</v>
+        <v>100.911</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>20.9</v>
+        <v>-1</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N87" t="n">
-        <v>102814.99</v>
+        <v>97177.83</v>
       </c>
       <c r="O87" t="n">
-        <v>124303.33</v>
+        <v>96206.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7247,95 +7230,203 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>5</v>
       </c>
       <c r="G88" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H88" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="J88" t="n">
-        <v>123.03</v>
+        <v>100.621</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v>-1</v>
+        <v>6.8696</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>6.8696</v>
       </c>
       <c r="N88" t="n">
-        <v>100000</v>
+        <v>96206.05</v>
       </c>
       <c r="O88" t="n">
-        <v>99000</v>
+        <v>102814.99</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H89" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J89" t="n">
+        <v>99.739</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N89" t="n">
+        <v>102814.99</v>
+      </c>
+      <c r="O89" t="n">
+        <v>124303.33</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H90" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J90" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O90" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
         <v>2</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F91" t="n">
         <v>2</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G91" t="n">
         <v>130.16</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H91" t="n">
         <v>130.94</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J91" t="n">
         <v>139.27</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="L89" t="n">
+      <c r="L91" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M89" s="5" t="n">
+      <c r="M91" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N91" t="n">
         <v>99000</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O91" t="n">
         <v>87437.31</v>
       </c>
     </row>
